--- a/Scraping/Inbreeding_FPHYS/JUPITER_PIPILINE/FPhys_phd_plus_headers.xlsx
+++ b/Scraping/Inbreeding_FPHYS/JUPITER_PIPILINE/FPhys_phd_plus_headers.xlsx
@@ -1206,67 +1206,29 @@
           <t>https://ras.nacid.bg/dissertation-preview/26249</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОНС "доктор" </t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1. Физически науки Специалност: Ядрена физика (вкл. ядрени модели и структура на атомното ядро; свойства на атомните ядра и експериментална ядрена техника; ядрени реакции и физика на деленето - радиоактивност) </t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29108 / 07.06.2004, утвърдено с Протокол No/дата: 4-06 / 23.03.2004 </t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07.06.2004 </t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Високо-спинови състояния в ядрата 108,110 Рd, получени като фрагменти на делене. Ефекти на смесване между основната и гама-ивицата Покажи повече информация </t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Асистент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 10.05.2017</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Асистент - Софийски университет "Св. Климент Охридски", 22.01.2004</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Locator.wait_for: Timeout 30000ms exceeded.
+Call log:
+  - waiting for locator("h4.panel-title").filter(has_text="Научни степени") to be visible
+Locator.wait_for: Timeout 60000ms exceeded.
+Call log:
+  - waiting for get_by_text("Настоящи академични длъжности").first to be visible
+</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1287,24 +1249,13 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 23.01.2013</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Locator.wait_for: Timeout 60000ms exceeded.
-Call log:
-  - waiting for locator("h4.panel-title").filter(has_text="Научни степени").locator("../following-sibling::div[1]").locator("div.panel-default").first.get_by_text("Диплома No/дата:") to be visible
-</t>
+          <t>Error: Timeout waiting for page to be loaded</t>
         </is>
       </c>
     </row>
@@ -1319,59 +1270,23 @@
           <t>https://ras.nacid.bg/dissertation-preview/29890</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОНС "доктор" </t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1. Физически науки Специалност: Ядрена физика (вкл. ядрени модели и структура на атомното ядро; свойства на атомните ядра и експериментална ядрена техника; ядрени реакции и физика на деленето - радиоактивност) </t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29541 / 21.02.2005, утвърдено с Протокол No/дата: 15-06 / 07.12.2004 </t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21.02.2005 </t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Структура на високоспинови състояния в ядра с маса-190:заселване на изомери в реакции на фрагментация и времена на живот в магнитни ивици Покажи повече информация </t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 07.02.2013</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Error: Timeout waiting for page to be loaded</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1384,59 +1299,23 @@
           <t>https://ras.nacid.bg/dissertation-preview/30909</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОНС "доктор" </t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1. Физически науки Специалност: Физика на елементарните частици и високите енергии (вкл. модели на взаимодействие и систематика на елементарните частици; структура и свойства на елементарните частици и резонанси; конкретни реакции и феноменология; експериментална техника на високите енергии; физика на космическите лъчи) </t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32533 / 21.07.2008, утвърдено с Протокол No/дата: 5-06 / 20.05.2008 </t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21.07.2008 </t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разработване и изследване на характеристиките на камери със съпротивителна плоскост за детектора CMS Покажи повече информация </t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 07.03.2014</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Error: Timeout waiting for page to be loaded</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1449,67 +1328,23 @@
           <t>https://ras.nacid.bg/dissertation-preview/27272</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ОНС "доктор" </t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.1. Физически науки Специалност: Физика на елементарните частици и високите енергии (вкл. модели на взаимодействие и систематика на елементарните частици; структура и свойства на елементарните частици и резонанси; конкретни реакции и феноменология; експериментална техника на високите енергии; физика на космическите лъчи) </t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32636 / 18.08.2008, утвърдено с Протокол No/дата: 7-06 / 17.06.2008 </t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18.08.2008 </t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Изследване на редки полулептонни разпада на К-мезони Покажи повече информация </t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Асистент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 08.04.2016</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Асистент - Софийски университет "Св. Климент Охридски", 19.11.2007</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Error: Timeout waiting for page to be loaded</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2608,24 +2443,16 @@
           <t xml:space="preserve">Числено изследване на басейнови и синоптични колебания в Черно море Покажи повече информация </t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Доцент - ВАК</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 19.05.2008</t>
-        </is>
-      </c>
+          <t>Доцент - ВАК | Доцент - Софийски университет "Св. Климент Охридски"</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Доцент - ВАК, 12.05.2008</t>
+          <t>Доцент - ВАК, 12.05.2008 | Доцент - Софийски университет "Св. Климент Охридски", 19.05.2008</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -6293,24 +6120,16 @@
           <t xml:space="preserve">Динамика на квазичастици в модели на силно корелирани електрони в теорията на високотемпературната свръхпроводимост Покажи повече информация </t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски"</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Главен асистент - Софийски университет "Св. Климент Охридски" | Доцент - ВАК</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Доцент - Софийски университет "Св. Климент Охридски", 03.11.2000</t>
-        </is>
-      </c>
+          <t>Главен асистент - Софийски университет "Св. Климент Охридски" | Доцент - ВАК | Доцент - Софийски университет "Св. Климент Охридски"</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Главен асистент - Софийски университет "Св. Климент Охридски", 30.10.1990 | Доцент - ВАК, 01.09.2000</t>
+          <t>Главен асистент - Софийски университет "Св. Климент Охридски", 30.10.1990 | Доцент - ВАК, 01.09.2000 | Доцент - Софийски университет "Св. Климент Охридски", 03.11.2000</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
@@ -8046,18 +7865,18 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
         <is>
           <t>Асистент - Софийски университет "Св. Климент Охридски"</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
         <is>
           <t>Асистент - Софийски университет "Св. Климент Охридски", 07.03.2024</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
